--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,14 +737,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45163.60887392885</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -787,15 +783,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="C21" s="19" t="n"/>
     </row>
@@ -846,7 +833,7 @@
       </c>
       <c r="C26" s="39" t="n"/>
       <c r="D26" s="41" t="n">
-        <v>252.96</v>
+        <v>281</v>
       </c>
       <c r="E26" s="42" t="n"/>
     </row>
@@ -857,7 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="17">
       <c r="A29" s="31" t="n"/>
       <c r="B29" s="31" t="n"/>
@@ -870,21 +856,15 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" s="17"/>
     <row r="32" ht="16.5" customHeight="1" s="17"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="19.5" customHeight="1" s="17">
       <c r="A36" s="7" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="6" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="25" t="inlineStr">
         <is>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -874,14 +874,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -874,14 +874,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45239</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45244</v>
+        <v>45245</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45245</v>
+        <v>45251</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -874,14 +874,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45251</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -874,14 +874,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -874,14 +874,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/LLANAS DISMAY.xlsx
+++ b/LISTAS/ma/LLANAS DISMAY.xlsx
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
